--- a/华风数据-初审-itss3/华风数据现场签到人员表.xlsx
+++ b/华风数据-初审-itss3/华风数据现场签到人员表.xlsx
@@ -78,7 +78,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,7 +553,7 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
@@ -554,57 +561,57 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
@@ -1147,7 +1154,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9.02777777777778" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="20.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="20.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
